--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>Pass and Failure Reason</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,6 +520,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -563,6 +573,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -611,6 +626,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,6 +679,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -707,6 +732,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -755,6 +785,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -803,6 +838,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -851,6 +891,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -899,6 +944,11 @@
           <t>Chatbot response was empty or contained an error.</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -945,6 +995,11 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>Chatbot response was empty or contained an error.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Match Percentage</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Hallucination</t>
         </is>
       </c>
@@ -522,6 +527,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -575,6 +585,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -628,6 +643,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -681,6 +701,11 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -734,6 +759,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -787,6 +817,11 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -840,6 +875,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -893,6 +933,11 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -946,6 +991,11 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
@@ -998,6 +1048,11 @@
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -509,7 +509,17 @@
           <t>Sportime offers a variety of sports and activities, including fitness and wellness classes, kids and youth programs, martial arts, swimming, tennis, and other recreational activities. Examples include yoga, Pilates, cycling, karate, swim lessons, tennis programs, and children’s activities.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@5e1dde44
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -522,17 +532,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 1.15% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -567,7 +577,17 @@
           <t>Trial sessions are available by providing your name, contact details, preferred activity, and availability to the front desk, who will match you with a class and answer questions.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@1ddc6db2
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -580,17 +600,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 3.03% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -625,7 +645,17 @@
           <t>To book a trial session, give the front desk your name, contact details, desired activity, and availability so they can schedule your class.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@5b8572df
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -638,17 +668,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 1.42% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -683,7 +713,17 @@
           <t>Call the club's phone number to sign up for trials, inquire about schedules and pricing, or book classes through the front desk.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@77c66a4f
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -696,17 +736,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.71% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -741,7 +781,17 @@
           <t>To help you, please share which specific activity or class you are interested in (such as yoga, karate, swimming, or cycling).</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@1930a804
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -754,17 +804,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 1.43% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -799,7 +849,17 @@
           <t>The fee structure depends on the selected classes.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@598778cc
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -812,17 +872,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.15% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -857,7 +917,17 @@
           <t>Ok fine.Feel free to reach out anytime if further assistance is needed.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@7286827b
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -870,17 +940,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.60% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -915,7 +985,17 @@
           <t>I need For details on single-day guest passes and guest policies,</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@25bc65ab
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -928,17 +1008,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.45% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -973,7 +1053,17 @@
           <t>Is there anything else you'd like to know about the clubi need information about  bringing multiple people at the same time. and specific guest policy details i can put this ?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@34d11c92
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -986,17 +1076,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.69% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1121,17 @@
           <t>Yes,multiple family members on the same account can check in together, and the front desk can assist with setting up family memberships or answering specific policy questions.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@138b9abe
+(tried for 45 seconds with 500 milliseconds interval)
+Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Irrelevant</t>
@@ -1044,17 +1144,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Chatbot response was empty or contained an error.</t>
+          <t>Match percentage is 0.97% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@5e1dde44
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@54402c04
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@1ddc6db2
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@642a16aa
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@5b8572df
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@b0f2d91
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@77c66a4f
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@77c66a4f
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@1930a804
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@5fb07347
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@598778cc
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@1fa9692b
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@7286827b
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@24068086
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@25bc65ab
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@7ca0166c
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@34d11c92
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@c7269ad
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc25040b950@138b9abe
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@662d3e85
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37481}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37481/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 459dc740ec2dc9eb231b85472b9d1ef1</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@54402c04
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@5434e40c
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@642a16aa
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@3b332962
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@b0f2d91
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@bc09d57
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@77c66a4f
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@73e1ecd0
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@5fb07347
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@677cc4e8
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@1fa9692b
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@3c346c45
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@24068086
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@43778371
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@7ca0166c
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@b90c5a5
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@c7269ad
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@18f27a81
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f86f040b950@662d3e85
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@19855799
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42961}, goog:processID: 2278, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42961/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 2c0334bdb7756f49ef070f6060c42dd6</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8806e47075646bfc77e028aef8b35308</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@5434e40c
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@54402c04
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@3b332962
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@642a16aa
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@bc09d57
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@44592c39
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@73e1ecd0
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@9690008
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Match percentage is 0.71% (&lt; 70% threshold required for passing).</t>
+          <t>Match percentage is 0.72% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@677cc4e8
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3b57f915
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@3c346c45
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@38cf3ae1
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@43778371
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@55682482
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@b90c5a5
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3a12f3e7
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@18f27a81
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3ef396c9
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f36b840b950@19855799
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@4a9412c4
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:33163}, goog:processID: 2663, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:33163/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8806e47075646bfc77e028aef8b35308</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@54402c04
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@5434e40c
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@642a16aa
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@3b332962
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@44592c39
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@bc09d57
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@9690008
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@73e1ecd0
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Match percentage is 0.72% (&lt; 70% threshold required for passing).</t>
+          <t>Match percentage is 0.71% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3b57f915
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@c732e1c
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@38cf3ae1
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@349f3ff7
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@55682482
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@3bf01a01
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3a12f3e7
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@5ebe903a
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@3ef396c9
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@7646c9f5
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fd27440b950@4a9412c4
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@486bcaa
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:32965}, goog:processID: 2619, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:32965/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 3e5c93b05dd8dc7d19f68509f4efda0f</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@5434e40c
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@54402c04
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@3b332962
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@642a16aa
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@bc09d57
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@44592c39
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@73e1ecd0
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@9690008
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Match percentage is 0.71% (&lt; 70% threshold required for passing).</t>
+          <t>Match percentage is 0.72% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@c732e1c
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@3b57f915
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@349f3ff7
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@2c0dca15
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@3bf01a01
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@56499781
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@5ebe903a
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@44864ebe
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@7646c9f5
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@568c9ee1
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fc37840b950@486bcaa
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@2ce62e27
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:37909}, goog:processID: 2512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:37909/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 1bddd4dac9d50eedb29f3b1e93fab271</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f5ae26e04e3641d25c156399b31cd401</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -511,13 +511,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@54402c04
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@5434e40c
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -579,13 +579,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@642a16aa
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@3b332962
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,13 +647,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@44592c39
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@bc09d57
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@9690008
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@73e1ecd0
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Match percentage is 0.72% (&lt; 70% threshold required for passing).</t>
+          <t>Match percentage is 0.71% (&lt; 70% threshold required for passing).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -783,13 +783,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@3b57f915
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@677cc4e8
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,13 +851,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@2c0dca15
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@3c346c45
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,13 +919,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@56499781
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@43778371
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,13 +987,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@44864ebe
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@2cacd55e
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,13 +1055,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@568c9ee1
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@31a024ea
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007f430840b950@2ce62e27
+          <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.ChatbotTest$$Lambda/0x00007fb3a840b950@7c857e8f
 (tried for 45 seconds with 500 milliseconds interval)
 Build info: version: '4.49.0', revision: 'bedb24f bedb24f6f703876e7e4c5d506f0d697eb358c720'
 System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:41171}, goog:processID: 2530, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:41171/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: f5ae26e04e3641d25c156399b31cd401</t>
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:45461}, goog:processID: 2405, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:45461/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 881c227d0d85c749867366d361532013</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Skipped - Missing Input File</t>
+          <t>Skipped - Missing API Key</t>
         </is>
       </c>
     </row>

--- a/Frameworks-Result.xlsx
+++ b/Frameworks-Result.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Skipped - Missing API Key</t>
+          <t>Skipped - Missing Input File</t>
         </is>
       </c>
     </row>
